--- a/Entrega/MedidasRedesPracticaMMS-I-1.xlsx
+++ b/Entrega/MedidasRedesPracticaMMS-I-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f53c128df0648ac2/Documentos/Estudios/DATCOM/2º Cuatrimestre/Minería de Medios Sociales/SeñorDeLosAnillos/Entrega/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{0481310F-A15A-4C69-A7A4-DC0F7C3E07CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2989C471-0DAD-4359-8221-8AFE035D72E1}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="8_{0481310F-A15A-4C69-A7A4-DC0F7C3E07CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DB0B246-45F2-49F8-9946-89DCDED4F983}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,12 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="145621"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="108">
   <si>
     <t xml:space="preserve">Nombre y apellidos del alumno: </t>
   </si>
@@ -422,12 +423,105 @@
   <si>
     <t>7.97%</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Análisis Comunidades </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Las Dos Torres</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>0.405</t>
+  </si>
+  <si>
+    <t>0.408</t>
+  </si>
+  <si>
+    <t>0.377</t>
+  </si>
+  <si>
+    <t>0.362</t>
+  </si>
+  <si>
+    <t>0.381</t>
+  </si>
+  <si>
+    <t>0.407</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>0.397</t>
+  </si>
+  <si>
+    <t>0.401</t>
+  </si>
+  <si>
+    <t>32.2%</t>
+  </si>
+  <si>
+    <t>16.15%</t>
+  </si>
+  <si>
+    <t>44.07%</t>
+  </si>
+  <si>
+    <t>26.71%</t>
+  </si>
+  <si>
+    <t>9.32%</t>
+  </si>
+  <si>
+    <t>18.64%</t>
+  </si>
+  <si>
+    <t>3.39%</t>
+  </si>
+  <si>
+    <t>0.31%</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>1.69%</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,6 +581,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -786,18 +888,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -814,6 +918,115 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>4763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1309688</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>55563</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA93D7F4-D0BC-0549-0CE7-F3DA68D30D45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3886201"/>
+          <a:ext cx="4576763" cy="3051175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1109662</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A205AF0-0DAB-2722-2D9F-9042B5A7DE9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7681913"/>
+          <a:ext cx="5715000" cy="3810000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1103,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="45.73046875" customWidth="1"/>
@@ -1224,7 +1437,7 @@
       <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="22">
         <v>2242</v>
       </c>
       <c r="C11" s="1"/>
@@ -1326,573 +1539,911 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A22" s="7" t="s">
+    <row r="21" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="22" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="23" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="26" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="27" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="28" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="29" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="31" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="33" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="34" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="35" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A37" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="3" t="s">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="39" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="40" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="41" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="42" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="43" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="44" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="45" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="46" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="47" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="48" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="49" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="50" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="51" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="52" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="53" spans="1:6" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.5"/>
+    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B60" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C60" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D60" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A27" s="13" t="s">
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A61" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B61" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C61" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D61" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A28" s="12" t="s">
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A62" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B62" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C62" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D62" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A29" s="12" t="s">
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A63" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B63" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C63" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D63" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A30" s="12" t="s">
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A64" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B64" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C64" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D64" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A31" s="12" t="s">
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A65" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B65" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C65" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D65" s="12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A32" s="12" t="s">
+    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A66" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B66" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C66" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D66" s="12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A33" s="12" t="s">
+    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A67" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B67" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C67" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D67" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A34" s="12" t="s">
+    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A68" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B68" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C68" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D68" s="12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A35" s="12" t="s">
+    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A69" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B69" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C69" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D69" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A36" s="12" t="s">
+    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A70" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B70" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C70" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D70" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-    </row>
-    <row r="40" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="41" spans="1:4" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="16" t="s">
+    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="75" spans="1:4" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A75" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B75" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C75" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D75" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="18" t="s">
+    <row r="76" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A76" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B76" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C76" s="19">
         <v>15</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D76" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A43" s="18" t="s">
+    <row r="77" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A77" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B77" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C77" s="19">
         <v>8</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D77" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A44" s="18" t="s">
+    <row r="78" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A78" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B78" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="19">
+      <c r="C78" s="19">
         <v>8</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D78" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A45" s="18" t="s">
+    <row r="79" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A79" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B79" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="19">
+      <c r="C79" s="19">
         <v>6</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D79" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A46" s="18">
+    <row r="80" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A80" s="18">
         <v>1</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B80" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C80" s="19">
         <v>6</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D80" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A47" s="18">
+    <row r="81" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A81" s="18">
         <v>1</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B81" s="19">
         <v>0.23499999999999999</v>
       </c>
-      <c r="C47" s="19">
+      <c r="C81" s="19">
         <v>5</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D81" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A48" s="18">
+    <row r="82" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A82" s="18">
         <v>1</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B82" s="19">
         <v>0.26500000000000001</v>
       </c>
-      <c r="C48" s="19">
+      <c r="C82" s="19">
         <v>7</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D82" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A49" s="18">
+    <row r="83" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A83" s="18">
         <v>1</v>
       </c>
-      <c r="B49" s="19" t="s">
+      <c r="B83" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C49" s="19">
+      <c r="C83" s="19">
         <v>7</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D83" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A50" s="18" t="s">
+    <row r="84" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A84" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B84" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="19">
+      <c r="C84" s="19">
         <v>4</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D84" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A51" s="18" t="s">
+    <row r="85" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A85" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B85" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C51" s="19">
+      <c r="C85" s="19">
         <v>4</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D85" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A52" s="18" t="s">
+    <row r="86" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A86" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B86" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="19">
+      <c r="C86" s="19">
         <v>3</v>
       </c>
-      <c r="D52" s="19" t="s">
+      <c r="D86" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A53" s="18" t="s">
+    <row r="87" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A87" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B53" s="19" t="s">
+      <c r="B87" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C53" s="19">
+      <c r="C87" s="19">
         <v>4</v>
       </c>
-      <c r="D53" s="19" t="s">
+      <c r="D87" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A54" s="26"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-    </row>
-    <row r="57" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.45">
-      <c r="A58" s="22" t="s">
+    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A88" s="23"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+    </row>
+    <row r="91" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A92" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B58" s="22" t="s">
+      <c r="B92" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="22" t="s">
+      <c r="C92" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D92" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E58" s="22" t="s">
+      <c r="E92" s="25" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A59" s="23"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="21" t="s">
+    <row r="93" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A93" s="26"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E59" s="23"/>
-    </row>
-    <row r="60" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A60" s="18" t="s">
+      <c r="E93" s="26"/>
+    </row>
+    <row r="94" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A94" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B60" s="19">
+      <c r="B94" s="19">
         <v>29</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C94" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D94" s="19">
         <v>101</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="E94" s="19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A61" s="18" t="s">
+    <row r="95" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A95" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B61" s="19">
+      <c r="B95" s="19">
         <v>34</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="C95" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D95" s="19">
         <v>100</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="E95" s="19" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A62" s="18" t="s">
+    <row r="96" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A96" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="19">
+      <c r="B96" s="19">
         <v>21</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C96" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D96" s="19">
         <v>106</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="E96" s="19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A63" s="18" t="s">
+    <row r="97" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A97" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B97" s="19">
         <v>17</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C97" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D97" s="19">
         <v>52</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E97" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A64" s="18" t="s">
+    <row r="98" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A98" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B98" s="19">
         <v>14</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C98" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D98" s="19">
         <v>32</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E98" s="19" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A65" s="18" t="s">
+    <row r="99" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A99" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B65" s="19">
+      <c r="B99" s="19">
         <v>10</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C99" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D99" s="19">
         <v>22</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="E99" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A66" s="18" t="s">
+    <row r="100" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A100" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="B66" s="19">
+      <c r="B100" s="19">
         <v>11</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="C100" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D100" s="19">
         <v>23</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="E100" s="19" t="s">
         <v>86</v>
       </c>
     </row>
+    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A103" s="24" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="105" spans="1:5" ht="31.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A105" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B105" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D105" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A106" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C106" s="19">
+        <v>8</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A107" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C107" s="19">
+        <v>9</v>
+      </c>
+      <c r="D107" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A108" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C108" s="19">
+        <v>8</v>
+      </c>
+      <c r="D108" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A109" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C109" s="19">
+        <v>6</v>
+      </c>
+      <c r="D109" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A110" s="18">
+        <v>1</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C110" s="19">
+        <v>5</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A111" s="18">
+        <v>1</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C111" s="19">
+        <v>5</v>
+      </c>
+      <c r="D111" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A112" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C112" s="19">
+        <v>4</v>
+      </c>
+      <c r="D112" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A113" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C113" s="19">
+        <v>4</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A114" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C114" s="19">
+        <v>5</v>
+      </c>
+      <c r="D114" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A115" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C115" s="19">
+        <v>4</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A116" s="23"/>
+      <c r="B116" s="23"/>
+      <c r="C116" s="23"/>
+      <c r="D116" s="23"/>
+    </row>
+    <row r="119" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A120" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B120" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E120" s="25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A121" s="26"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="26"/>
+      <c r="D121" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E121" s="26"/>
+    </row>
+    <row r="122" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A122" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B122" s="19">
+        <v>19</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D122" s="19">
+        <v>52</v>
+      </c>
+      <c r="E122" s="19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A123" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" s="19">
+        <v>26</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D123" s="19">
+        <v>86</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A124" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B124" s="19">
+        <v>11</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D124" s="19">
+        <v>30</v>
+      </c>
+      <c r="E124" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A125" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B125" s="19">
+        <v>2</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D125" s="19">
+        <v>1</v>
+      </c>
+      <c r="E125" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A126" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B126" s="19">
+        <v>1</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D126" s="19">
+        <v>0</v>
+      </c>
+      <c r="E126" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="E58:E59"/>
+  <mergeCells count="8">
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="E120:E121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>